--- a/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_GA.xlsx
+++ b/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_GA.xlsx
@@ -2,27 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="R54df1cf76be74e16"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="R03f3efd6cf6c4d7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="R230b70da2716421c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="Rcdeb4a02a01f484a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="R685c0d0433ef4309"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="Rb7514ca38e1f4e37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="Rf608adf8da424df2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="R7f7e0a3204a34b55"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="R71083fea25974abe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="Rb7d0711c9ceb4634"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="Ree3235a1c72f4878"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="R3485dfc6469e4d7d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="R7b6dca6777c848b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="Rcb2edbebdeca4fb0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="Rfd2a46030ac147ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="R9cd8cc0e276e4d4f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="R89d01990e87e468b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="R8d92c9a81f904373"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="R3323845a95834a90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="Rcba08719dea04a80"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="R8b37dd23265b4e55"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="R7e00f87332a24531"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="Rd99d5e1aea6e4427"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="R8b249df649b04694"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="Rde3f411dd65c4f54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="R1f63fa2db6c1480e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="R45b9e79aa8034023"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="R24eb6ac0848d4769"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="R0e504bdb7df942b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="R41b3474775da4cde"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="Ra48426545e754b9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="Ra690e6b851a04974"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="R947731861de64428"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="R97a68e91e05d4d00"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="Rfdfd8bc3c9f14383"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="Raaa2046978834533"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="Rcc70c02649d74e32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="R079ed04925164472"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="R5aa0cf5c54224e91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="Rc7c29d05bfdd4d1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="R6951f6525ac1459c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="Rba7595424b0842dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロフィール" sheetId="22" r:id="R945c87c91de748de"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4355,6 +4356,41 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="13.75" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="51.25" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="19.5" customHeight="1">
+      <x:c r="A1" t="str">
+        <x:v>名前</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>チャルガ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="19.5" customHeight="1">
+      <x:c r="A2" t="str">
+        <x:v>出身地</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>ゲハク平原</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="19.5" customHeight="1">
+      <x:c r="A3" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c r="B3"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
